--- a/output/2026-09-13_14_Croazia_Bjelovarsko-bilogorska_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-13_14_Croazia_Bjelovarsko-bilogorska_Impiantistica_aspirazione_industriale.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
